--- a/backend-excel/data/accounts.xlsx
+++ b/backend-excel/data/accounts.xlsx
@@ -401,19 +401,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>id</v>
+        <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>username</v>
+        <v>USERNAME</v>
       </c>
       <c r="C1" t="str">
-        <v>password</v>
+        <v>PASSWORD</v>
       </c>
       <c r="D1" t="str">
-        <v>fullName</v>
+        <v>FULLNAME</v>
       </c>
       <c r="E1" t="str">
-        <v>role</v>
+        <v>ROLE</v>
       </c>
     </row>
     <row r="2">
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$tPK.2/OrZUTSIq4WOSEuu.me1ERTrDYgLvEWS3PdBUQQSgt05JsWW</v>
+        <v>$2a$10$6HspttK4awNpNyaz0uVHpeaoN9cFQdoImjH9518tbhg09zY/Lc1UO</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,10 +441,10 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$1Y53qXf7Yi2rSnwmJhAycep3l4d0c8jiUgAJw7w6e6JIRhWbe.2wW</v>
+        <v>$2a$10$uUaitW12.mQanftv0aN6ieWbceceQ12qJqjt9t2oOiPGgebWHc3Z.</v>
       </c>
       <c r="D3" t="str">
-        <v>luanluan</v>
+        <v>Lê Công Trân</v>
       </c>
       <c r="E3" t="str">
         <v>admin</v>
@@ -452,16 +452,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>929c7d1f-bc0d-47c9-882f-45df51dd58b6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>luanluan</v>
+        <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$zXw4Db3L07AJrdkohNG6ceQrIBXl.QdB4y5Ctyf4pxiyQBgTNOb2y</v>
+        <v>$2a$10$7KH/Jm9WzgTaS9W0J1PVqOi0suLvlkSvdxG3f0P6rofSPszr9bEV6</v>
       </c>
       <c r="D4" t="str">
-        <v>luan long an</v>
+        <v>Nguyễn Thị Cam</v>
       </c>
       <c r="E4" t="str">
         <v>user</v>

--- a/backend-excel/data/accounts.xlsx
+++ b/backend-excel/data/accounts.xlsx
@@ -1,41 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lctran\wc2026-bet\bet-wc2026\backend-excel\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371C9B7B-1741-4C8B-B314-D04A3CF66BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="accounts" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>USERNAME</t>
+  </si>
+  <si>
+    <t>PASSWORD</t>
+  </si>
+  <si>
+    <t>FULLNAME</t>
+  </si>
+  <si>
+    <t>ROLE</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>$2a$10$6HspttK4awNpNyaz0uVHpeaoN9cFQdoImjH9518tbhg09zY/Lc1UO</t>
+  </si>
+  <si>
+    <t>Administrator</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>lctran</t>
+  </si>
+  <si>
+    <t>$2a$10$uUaitW12.mQanftv0aN6ieWbceceQ12qJqjt9t2oOiPGgebWHc3Z.</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>$2a$10$7KH/Jm9WzgTaS9W0J1PVqOi0suLvlkSvdxG3f0P6rofSPszr9bEV6</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>Tran Chanh Luan</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +107,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,80 +446,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="47.296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>USERNAME</v>
-      </c>
-      <c r="C1" t="str">
-        <v>PASSWORD</v>
-      </c>
-      <c r="D1" t="str">
-        <v>FULLNAME</v>
-      </c>
-      <c r="E1" t="str">
-        <v>ROLE</v>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>admin</v>
-      </c>
-      <c r="C2" t="str">
-        <v>$2a$10$6HspttK4awNpNyaz0uVHpeaoN9cFQdoImjH9518tbhg09zY/Lc1UO</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Administrator</v>
-      </c>
-      <c r="E2" t="str">
-        <v>admin</v>
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>lctran</v>
-      </c>
-      <c r="C3" t="str">
-        <v>$2a$10$uUaitW12.mQanftv0aN6ieWbceceQ12qJqjt9t2oOiPGgebWHc3Z.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Lê Công Trân</v>
-      </c>
-      <c r="E3" t="str">
-        <v>admin</v>
+    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>cam</v>
-      </c>
-      <c r="C4" t="str">
-        <v>$2a$10$7KH/Jm9WzgTaS9W0J1PVqOi0suLvlkSvdxG3f0P6rofSPszr9bEV6</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Nguyễn Thị Cam</v>
-      </c>
-      <c r="E4" t="str">
-        <v>user</v>
+    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError sqref="A1:E2 A4 A3:C3 E3 E4 C4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend-excel/data/accounts.xlsx
+++ b/backend-excel/data/accounts.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$6HspttK4awNpNyaz0uVHpeaoN9cFQdoImjH9518tbhg09zY/Lc1UO</v>
+        <v>$2a$10$m.V0ePQMPyfi4PSrJK4bTuPWlZyW/CldaCXesSQjcFZb3paR/A8Vu</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,7 +441,7 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$uUaitW12.mQanftv0aN6ieWbceceQ12qJqjt9t2oOiPGgebWHc3Z.</v>
+        <v>$2a$10$6HzC3pOlWTWRH19z5exDs.1DfaTl5/zNbsqdF4Z0iNjtsYKdsjnDS</v>
       </c>
       <c r="D3" t="str">
         <v>Lê Công Trân</v>
@@ -458,7 +458,7 @@
         <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$7KH/Jm9WzgTaS9W0J1PVqOi0suLvlkSvdxG3f0P6rofSPszr9bEV6</v>
+        <v>$2a$10$PkawQN/jw9d9zwErPOBQ8uPdsgywg6ktRlaH/kngzgBTs8GGycSdi</v>
       </c>
       <c r="D4" t="str">
         <v>Nguyễn Thị Cam</v>

--- a/backend-excel/data/accounts.xlsx
+++ b/backend-excel/data/accounts.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$6HspttK4awNpNyaz0uVHpeaoN9cFQdoImjH9518tbhg09zY/Lc1UO</v>
+        <v>$2a$10$TbKN0dEKURg14kYcVgXiYu2pTkxakk4HBie.umFrWdAgdiZWFKbMi</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,7 +441,7 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$uUaitW12.mQanftv0aN6ieWbceceQ12qJqjt9t2oOiPGgebWHc3Z.</v>
+        <v>$2a$10$.aq9vYRe8P59YMXHabrROuSHvgyXhxUABop.67XnSKBNsIMVNDPIy</v>
       </c>
       <c r="D3" t="str">
         <v>Tran Chanh Luan</v>
@@ -458,7 +458,7 @@
         <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$7KH/Jm9WzgTaS9W0J1PVqOi0suLvlkSvdxG3f0P6rofSPszr9bEV6</v>
+        <v>$2a$10$cegUMS9..lnU2gFKgmDKPuYzCeGOBLWeSiD.eM3GN.PzIC5hP8R8K</v>
       </c>
       <c r="D4" t="str">
         <v>Nguyễn Thị Cam</v>
@@ -475,7 +475,7 @@
         <v>test</v>
       </c>
       <c r="C5" t="str">
-        <v>$2a$10$7KH/Jm9WzgTaS9W0J1PVqOi0suLvlkSvdxG3f0P6rofSPszr9bEV6</v>
+        <v>$2a$10$Be5q9ZuOnHAMYT8Z3OAi/.8xtpIcuWPGe610ClsBNzACiNRWZrqfG</v>
       </c>
       <c r="D5" t="str">
         <v>test</v>

--- a/backend-excel/data/accounts.xlsx
+++ b/backend-excel/data/accounts.xlsx
@@ -1,41 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lctran\wc2026-bet\bet-wc2026\backend-excel\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9A254B-356C-41F9-86DD-7733AD99C102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="accounts" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>USERNAME</t>
+  </si>
+  <si>
+    <t>PASSWORD</t>
+  </si>
+  <si>
+    <t>FULLNAME</t>
+  </si>
+  <si>
+    <t>ROLE</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>$2a$10$s37Hj7N4qHuQye0OFn7abOBbCQeHhhm5LO0YahTv.GEtOgpMFUQ9u</t>
+  </si>
+  <si>
+    <t>Administrator</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>lctran</t>
+  </si>
+  <si>
+    <t>$2a$10$wuiKYzuSTyfa2aUWxEfq1umIh1OcNrNDPI1hODLZV13C8L3PC8wE.</t>
+  </si>
+  <si>
+    <t>Tran Chanh Luan</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>cam</t>
+  </si>
+  <si>
+    <t>$2a$10$9UlVbs6qO.99Bd4NIBE6GunoM6/lVIqkvYn/RY2CxCbRA21/BVk6O</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>$2a$10$hb/fGSTMVmSdaAuJFscqGec/PQEyzpw/7S0naJTFnFxeyIsUdLweW</t>
+  </si>
+  <si>
+    <t>Dao Quang Cam</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +119,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,97 +458,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="43.19921875" customWidth="1"/>
+    <col min="4" max="4" width="61.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>USERNAME</v>
-      </c>
-      <c r="C1" t="str">
-        <v>PASSWORD</v>
-      </c>
-      <c r="D1" t="str">
-        <v>FULLNAME</v>
-      </c>
-      <c r="E1" t="str">
-        <v>ROLE</v>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>admin</v>
-      </c>
-      <c r="C2" t="str">
-        <v>$2a$10$s37Hj7N4qHuQye0OFn7abOBbCQeHhhm5LO0YahTv.GEtOgpMFUQ9u</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Administrator</v>
-      </c>
-      <c r="E2" t="str">
-        <v>admin</v>
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>lctran</v>
-      </c>
-      <c r="C3" t="str">
-        <v>$2a$10$wuiKYzuSTyfa2aUWxEfq1umIh1OcNrNDPI1hODLZV13C8L3PC8wE.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Tran Chanh Luan</v>
-      </c>
-      <c r="E3" t="str">
-        <v>admin</v>
+    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>cam</v>
-      </c>
-      <c r="C4" t="str">
-        <v>$2a$10$9UlVbs6qO.99Bd4NIBE6GunoM6/lVIqkvYn/RY2CxCbRA21/BVk6O</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Nguyễn Thị Cam</v>
-      </c>
-      <c r="E4" t="str">
-        <v>user</v>
+    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>test</v>
-      </c>
-      <c r="C5" t="str">
-        <v>$2a$10$hb/fGSTMVmSdaAuJFscqGec/PQEyzpw/7S0naJTFnFxeyIsUdLweW</v>
-      </c>
-      <c r="D5" t="str">
-        <v>test</v>
-      </c>
-      <c r="E5" t="str">
-        <v>user</v>
+    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError sqref="A1:E3 A5:E5 A4:C4 E4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend-excel/data/accounts.xlsx
+++ b/backend-excel/data/accounts.xlsx
@@ -1,95 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lctran\wc2026-bet\bet-wc2026\backend-excel\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9A254B-356C-41F9-86DD-7733AD99C102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="accounts" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>USERNAME</t>
-  </si>
-  <si>
-    <t>PASSWORD</t>
-  </si>
-  <si>
-    <t>FULLNAME</t>
-  </si>
-  <si>
-    <t>ROLE</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>$2a$10$s37Hj7N4qHuQye0OFn7abOBbCQeHhhm5LO0YahTv.GEtOgpMFUQ9u</t>
-  </si>
-  <si>
-    <t>Administrator</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>lctran</t>
-  </si>
-  <si>
-    <t>$2a$10$wuiKYzuSTyfa2aUWxEfq1umIh1OcNrNDPI1hODLZV13C8L3PC8wE.</t>
-  </si>
-  <si>
-    <t>Tran Chanh Luan</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>cam</t>
-  </si>
-  <si>
-    <t>$2a$10$9UlVbs6qO.99Bd4NIBE6GunoM6/lVIqkvYn/RY2CxCbRA21/BVk6O</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>$2a$10$hb/fGSTMVmSdaAuJFscqGec/PQEyzpw/7S0naJTFnFxeyIsUdLweW</t>
-  </si>
-  <si>
-    <t>Dao Quang Cam</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -119,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -458,103 +396,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="43.19921875" customWidth="1"/>
-    <col min="4" max="4" width="61.5" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>USERNAME</v>
+      </c>
+      <c r="C1" t="str">
+        <v>PASSWORD</v>
+      </c>
+      <c r="D1" t="str">
+        <v>FULLNAME</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ROLE</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="str">
+        <v>admin</v>
+      </c>
+      <c r="C2" t="str">
+        <v>$2a$10$EJkfja8nUn0kWniVg2pkDeM79pnPKX3FHShg5z1s/Uq9/HkziDH4m</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="E2" t="str">
+        <v>admin</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="str">
+        <v>lctran</v>
+      </c>
+      <c r="C3" t="str">
+        <v>$2a$10$TLTlL/3URkhZHVk88894F.kwXo.zW78ww6vuCF5ZGvoBDxIZqIWFW</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Tran Chanh Luan</v>
+      </c>
+      <c r="E3" t="str">
+        <v>admin</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4" t="str">
+        <v>cam</v>
+      </c>
+      <c r="C4" t="str">
+        <v>$2a$10$QsjgAKA5loONjFUhCOGsd.uLSvGGr77rxN7Dl3C4mjgQ7S2Xi1a.2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Nguyễn Thị Cam</v>
+      </c>
+      <c r="E4" t="str">
+        <v>user</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
+      <c r="B5" t="str">
+        <v>test</v>
+      </c>
+      <c r="C5" t="str">
+        <v>$2a$10$jkQ3sMKkbhFANbhXoNuvs.PQdJmggra6rJ/dEnc0elYJJRYHdYJT6</v>
+      </c>
+      <c r="D5" t="str">
+        <v>test</v>
+      </c>
+      <c r="E5" t="str">
+        <v>user</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E3 A5:E5 A4:C4 E4" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend-excel/data/accounts.xlsx
+++ b/backend-excel/data/accounts.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$EJkfja8nUn0kWniVg2pkDeM79pnPKX3FHShg5z1s/Uq9/HkziDH4m</v>
+        <v>$2a$10$QUeBocwrNV.0rN8pLMtoMO/kNKUcQWZ9McuSUMJSfhM/7fxnwx3EW</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,7 +441,7 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$TLTlL/3URkhZHVk88894F.kwXo.zW78ww6vuCF5ZGvoBDxIZqIWFW</v>
+        <v>$2a$10$LzUY3..u62waWJwxfnLmt.3aJS2TOoqBB/882vD6FFQ6lU8WrdJQG</v>
       </c>
       <c r="D3" t="str">
         <v>Tran Chanh Luan</v>
@@ -458,7 +458,7 @@
         <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$QsjgAKA5loONjFUhCOGsd.uLSvGGr77rxN7Dl3C4mjgQ7S2Xi1a.2</v>
+        <v>$2a$10$uVHuCt3ymtm1UTOWzhhCeeNnB4xLekhWwvi.V0XrNseCt1Gm9D36O</v>
       </c>
       <c r="D4" t="str">
         <v>Nguyễn Thị Cam</v>
@@ -475,7 +475,7 @@
         <v>test</v>
       </c>
       <c r="C5" t="str">
-        <v>$2a$10$jkQ3sMKkbhFANbhXoNuvs.PQdJmggra6rJ/dEnc0elYJJRYHdYJT6</v>
+        <v>$2a$10$fmFbZJHw3HxoCdUCnVOJb.XzySL8e9RMHenN3vzg/bnj.b9IGn2J2</v>
       </c>
       <c r="D5" t="str">
         <v>test</v>

--- a/backend-excel/data/accounts.xlsx
+++ b/backend-excel/data/accounts.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$QUeBocwrNV.0rN8pLMtoMO/kNKUcQWZ9McuSUMJSfhM/7fxnwx3EW</v>
+        <v>$2a$10$9HpgCwgN3eI2m3PekH.Ztu9qot1hsC1kS8sFjBQdLkfktvUnBTsty</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,7 +441,7 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$LzUY3..u62waWJwxfnLmt.3aJS2TOoqBB/882vD6FFQ6lU8WrdJQG</v>
+        <v>$2a$10$D4VO3B7eplyFuAy7dth2aOO2H/a21VXEr2EhUNnVVzLxfzfFQk6k.</v>
       </c>
       <c r="D3" t="str">
         <v>Tran Chanh Luan</v>
@@ -458,7 +458,7 @@
         <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$uVHuCt3ymtm1UTOWzhhCeeNnB4xLekhWwvi.V0XrNseCt1Gm9D36O</v>
+        <v>$2a$10$IPt3KMUCnPt9zXMx9yZPp.8U.jOC1gMcrWbrDdNOlVQqmBp6xDhXa</v>
       </c>
       <c r="D4" t="str">
         <v>Nguyễn Thị Cam</v>
@@ -475,7 +475,7 @@
         <v>test</v>
       </c>
       <c r="C5" t="str">
-        <v>$2a$10$fmFbZJHw3HxoCdUCnVOJb.XzySL8e9RMHenN3vzg/bnj.b9IGn2J2</v>
+        <v>$2a$10$BApe2cDr5pl6tBiZzcD9LOLGVh6gcaXd8tdFgUg/S6CNs52UmHvMC</v>
       </c>
       <c r="D5" t="str">
         <v>test</v>

--- a/backend-excel/data/accounts.xlsx
+++ b/backend-excel/data/accounts.xlsx
@@ -424,7 +424,7 @@
         <v>admin</v>
       </c>
       <c r="C2" t="str">
-        <v>$2a$10$9HpgCwgN3eI2m3PekH.Ztu9qot1hsC1kS8sFjBQdLkfktvUnBTsty</v>
+        <v>$2a$10$9qbCwNF3M37kQGO2Q7A.meIpOdyZDf/AQB/tr6JI0efGsSx62rvwi</v>
       </c>
       <c r="D2" t="str">
         <v>Administrator</v>
@@ -441,7 +441,7 @@
         <v>lctran</v>
       </c>
       <c r="C3" t="str">
-        <v>$2a$10$D4VO3B7eplyFuAy7dth2aOO2H/a21VXEr2EhUNnVVzLxfzfFQk6k.</v>
+        <v>$2a$10$7102X88SMhaXjgvcS4uPNeKLDaB.BEuvYREwr0QMAlh7Ap1MQumdC</v>
       </c>
       <c r="D3" t="str">
         <v>Tran Chanh Luan</v>
@@ -458,7 +458,7 @@
         <v>cam</v>
       </c>
       <c r="C4" t="str">
-        <v>$2a$10$IPt3KMUCnPt9zXMx9yZPp.8U.jOC1gMcrWbrDdNOlVQqmBp6xDhXa</v>
+        <v>$2a$10$a2Nn2dlp6NDHGujxm0iKS.mcuD9CTI7zBszGftqYo8305rapG6ejO</v>
       </c>
       <c r="D4" t="str">
         <v>Nguyễn Thị Cam</v>
@@ -475,7 +475,7 @@
         <v>test</v>
       </c>
       <c r="C5" t="str">
-        <v>$2a$10$BApe2cDr5pl6tBiZzcD9LOLGVh6gcaXd8tdFgUg/S6CNs52UmHvMC</v>
+        <v>$2a$10$54LjT1jWokPyd5jdxHbJVOsB8NWv9h8BcGXu6mmaQcyn0KM6Hq1mS</v>
       </c>
       <c r="D5" t="str">
         <v>test</v>
